--- a/Intermediate Accounting Selected MCQs.xlsx
+++ b/Intermediate Accounting Selected MCQs.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Selected MCQs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Selected MCQs'!$A$1:$I$191</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Selected MCQs'!$A$1:$I$201</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I191"/>
+  <dimension ref="A1:I201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -18252,8 +18252,488 @@
         </is>
       </c>
     </row>
+    <row r="192" ht="90" customHeight="1">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>4. Time Value of Money</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>IA-TVM-01</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>Hartwell Company invests $20,000 today in a savings account that earns 6% interest compounded annually. How much will the account be worth at the end of 4 years?
+FV of $1 factor (6%, 4 periods): 1.26248</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>$25,250</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>$24,800</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>$20,000</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
+          <t>$24,000</t>
+        </is>
+      </c>
+      <c r="H192" s="2" t="inlineStr">
+        <is>
+          <t>A. $25,250</t>
+        </is>
+      </c>
+      <c r="I192" s="2" t="inlineStr">
+        <is>
+          <t>The future value of a single lump sum is calculated by multiplying the present amount by the FV of $1 factor: $20,000 × 1.26248 = $25,249.60, which rounds to $25,250 (Option A).
+Option B ($24,800) is wrong because it applies simple interest for 4 years rather than compounding: $20,000 × 0.06 × 4 = $4,800 of interest, giving $20,000 + $4,800 = $24,800. This ignores the compounding of interest on interest.
+Option C ($20,000) is wrong because it returns only the original principal with no growth applied—a fundamental conceptual error.
+Option D ($24,000) is wrong because it appears to apply a flat 20% total return (perhaps mistakenly using 5% × 4 years instead of 6% × 4 years under simple interest): $20,000 × 1.20 = $24,000. Neither the rate nor the compounding convention matches the problem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="90" customHeight="1">
+      <c r="A193" s="3" t="inlineStr">
+        <is>
+          <t>4. Time Value of Money</t>
+        </is>
+      </c>
+      <c r="B193" s="3" t="inlineStr">
+        <is>
+          <t>IA-TVM-02</t>
+        </is>
+      </c>
+      <c r="C193" s="3" t="inlineStr">
+        <is>
+          <t>Meridian Company will receive $50,000 in 5 years. The appropriate discount rate is 8% compounded annually. What is the present value of this future receipt today?
+PV of $1 factor (8%, 5 periods): 0.68058</t>
+        </is>
+      </c>
+      <c r="D193" s="3" t="inlineStr">
+        <is>
+          <t>$34,029</t>
+        </is>
+      </c>
+      <c r="E193" s="3" t="inlineStr">
+        <is>
+          <t>$50,000</t>
+        </is>
+      </c>
+      <c r="F193" s="3" t="inlineStr">
+        <is>
+          <t>$46,000</t>
+        </is>
+      </c>
+      <c r="G193" s="3" t="inlineStr">
+        <is>
+          <t>$32,000</t>
+        </is>
+      </c>
+      <c r="H193" s="3" t="inlineStr">
+        <is>
+          <t>A. $34,029</t>
+        </is>
+      </c>
+      <c r="I193" s="3" t="inlineStr">
+        <is>
+          <t>The present value of a single future amount is the future amount multiplied by the PV of $1 factor. $50,000 × 0.68058 = $34,029. Option B is wrong because it ignores discounting entirely and returns the undiscounted future amount. Option C is wrong because it subtracts only one period of simple interest ($50,000 × 8% × 1 = $4,000), which is not the correct discounting method. Option D is wrong because it uses a rough simple-interest deduction over all five periods ($50,000 − $50,000 × 8% × 5 = $30,000 is closer, but $32,000 reflects an arbitrary approximation that ignores compound discounting).</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="90" customHeight="1">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>4. Time Value of Money</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>IA-TVM-03</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>Two payment streams both consist of $5,000 per year for 6 years at a discount rate of 7%. Stream A payments occur at the end of each year (ordinary annuity). Stream B payments occur at the beginning of each year (annuity due). Which statement is correct?</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>Stream B has a higher present value because each payment is discounted for one fewer period.</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>Stream A has a higher present value because the payments last one additional period.</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>Both streams have the same present value because the total cash paid is identical.</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="inlineStr">
+        <is>
+          <t>Stream B has a lower present value because beginning-of-period payments carry more risk.</t>
+        </is>
+      </c>
+      <c r="H194" s="2" t="inlineStr">
+        <is>
+          <t>A. Stream B has a higher present value because each payment is discounted for one fewer period.</t>
+        </is>
+      </c>
+      <c r="I194" s="2" t="inlineStr">
+        <is>
+          <t>An annuity due (Stream B) has a higher present value than an otherwise identical ordinary annuity (Stream A) because each payment arrives one period earlier. Discounting each payment for one fewer period produces a larger present value. The annuity-due PV factor equals the ordinary-annuity PV factor multiplied by (1 + i). Option B is wrong because both streams contain the same number of payments; ordinary annuity payments are not spread over an extra period. Option C is wrong because timing differences cause present values to differ even when total cash is equal. Option D is wrong because receiving money sooner — not later — reduces discounting and increases present value; it has nothing to do with risk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="90" customHeight="1">
+      <c r="A195" s="3" t="inlineStr">
+        <is>
+          <t>4. Time Value of Money</t>
+        </is>
+      </c>
+      <c r="B195" s="3" t="inlineStr">
+        <is>
+          <t>IA-TVM-04</t>
+        </is>
+      </c>
+      <c r="C195" s="3" t="inlineStr">
+        <is>
+          <t>Each year for 5 years, Oakdale Company deposits $8,000 into a fund at the end of the year. The fund earns 5% interest compounded annually. What is the total accumulated balance in the fund at the end of Year 5?
+FV of ordinary annuity of $1 factor (5%, 5 periods): 5.52563</t>
+        </is>
+      </c>
+      <c r="D195" s="3" t="inlineStr">
+        <is>
+          <t>$44,205</t>
+        </is>
+      </c>
+      <c r="E195" s="3" t="inlineStr">
+        <is>
+          <t>$40,000</t>
+        </is>
+      </c>
+      <c r="F195" s="3" t="inlineStr">
+        <is>
+          <t>$42,000</t>
+        </is>
+      </c>
+      <c r="G195" s="3" t="inlineStr">
+        <is>
+          <t>$46,000</t>
+        </is>
+      </c>
+      <c r="H195" s="3" t="inlineStr">
+        <is>
+          <t>A. $44,205</t>
+        </is>
+      </c>
+      <c r="I195" s="3" t="inlineStr">
+        <is>
+          <t>The future value of an ordinary annuity equals the periodic payment multiplied by the FV of ordinary annuity factor. $8,000 × 5.52563 = $44,205.04, which rounds to $44,205. Option B is wrong because it sums only the deposits without adding any interest ($8,000 × 5 = $40,000). Option C is wrong because it adds a rough, understated interest estimate to the total deposits. Option D is wrong because it overstates the interest by applying the full 5% rate to all deposits for all five years simultaneously, ignoring that early deposits earn interest for more years than later deposits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="90" customHeight="1">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>4. Time Value of Money</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>IA-TVM-05</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>Crestview Company wins a legal settlement that will pay $15,000 at the end of each year for 6 years. The appropriate discount rate is 9% per year. What is the present value of the settlement today?
+PV of ordinary annuity of $1 factor (9%, 6 periods): 4.48592</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>$67,289</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>$90,000</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>$73,500</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="inlineStr">
+        <is>
+          <t>$62,000</t>
+        </is>
+      </c>
+      <c r="H196" s="2" t="inlineStr">
+        <is>
+          <t>A. $67,289</t>
+        </is>
+      </c>
+      <c r="I196" s="2" t="inlineStr">
+        <is>
+          <t>The present value of an ordinary annuity equals the periodic payment multiplied by the PV of ordinary annuity factor. $15,000 × 4.48592 = $67,288.80, which rounds to $67,289. Option B is wrong because it sums the undiscounted payments ($15,000 × 6 = $90,000) without applying any discounting. Option C is wrong because it applies an incorrect, lower annuity factor, understating the number of periods or the factor. Option D is wrong because it uses a PV of a single-sum factor instead of an annuity factor, treating the entire $90,000 as one lump sum discounted at an arbitrary rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" ht="90" customHeight="1">
+      <c r="A197" s="3" t="inlineStr">
+        <is>
+          <t>4. Time Value of Money</t>
+        </is>
+      </c>
+      <c r="B197" s="3" t="inlineStr">
+        <is>
+          <t>IA-TVM-07</t>
+        </is>
+      </c>
+      <c r="C197" s="3" t="inlineStr">
+        <is>
+          <t>Ridgeway Company will need $40,000 in 3 years. The account earns 10% per year compounded semiannually. What amount must Ridgeway deposit today to accumulate $40,000 at the end of 3 years?
+Factors for a single sum at 10% annually, 3 periods: 0.75131
+Factors for a single sum at 5% semiannually, 6 periods: 0.74622</t>
+        </is>
+      </c>
+      <c r="D197" s="3" t="inlineStr">
+        <is>
+          <t>$29,849</t>
+        </is>
+      </c>
+      <c r="E197" s="3" t="inlineStr">
+        <is>
+          <t>$30,052</t>
+        </is>
+      </c>
+      <c r="F197" s="3" t="inlineStr">
+        <is>
+          <t>$40,000</t>
+        </is>
+      </c>
+      <c r="G197" s="3" t="inlineStr">
+        <is>
+          <t>$36,000</t>
+        </is>
+      </c>
+      <c r="H197" s="3" t="inlineStr">
+        <is>
+          <t>A. $29,849</t>
+        </is>
+      </c>
+      <c r="I197" s="3" t="inlineStr">
+        <is>
+          <t>When compounding is semiannual, the periodic rate is the annual rate divided by 2 (10% / 2 = 5%) and the number of periods is years multiplied by 2 (3 × 2 = 6 periods). The correct PV factor is therefore the one at 5% for 6 periods: 0.74622. $40,000 × 0.74622 = $29,848.80, which rounds to $29,849. Option B is wrong because it uses the annual factor (10%, 3 periods: 0.75131), failing to adjust for semiannual compounding; $40,000 × 0.75131 = $30,052. Option C is wrong because it deposits the full future amount today with no discounting. Option D is wrong because it deducts only one period of simple interest ($40,000 × 10% = $4,000) from the future amount, which does not reflect proper discounting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="90" customHeight="1">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>2. Adjusting Journal Entries / Accounting Cycle</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>IA-AJE-01</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>On October 1, Year 1, Fernwood Company paid $9,600 for a 12-month insurance policy covering October 1, Year 1 through September 30, Year 2. The full premium was recorded as Prepaid Insurance on October 1. Fernwood's fiscal year ends December 31, Year 1. What is the correct adjusting journal entry on December 31, Year 1?</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>Debit Insurance Expense $2,400; Credit Prepaid Insurance $2,400</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>Debit Prepaid Insurance $2,400; Credit Insurance Expense $2,400</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>Debit Insurance Expense $9,600; Credit Prepaid Insurance $9,600</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="inlineStr">
+        <is>
+          <t>Debit Insurance Expense $7,200; Credit Prepaid Insurance $7,200</t>
+        </is>
+      </c>
+      <c r="H198" s="2" t="inlineStr">
+        <is>
+          <t>A. Debit Insurance Expense $2,400; Credit Prepaid Insurance $2,400</t>
+        </is>
+      </c>
+      <c r="I198" s="2" t="inlineStr">
+        <is>
+          <t>By December 31, Year 1, three months of the policy have elapsed (October, November, December). The expired portion is $9,600 × 3/12 = $2,400. The adjusting entry records the expense for the expired coverage and reduces Prepaid Insurance accordingly: debit Insurance Expense $2,400 and credit Prepaid Insurance $2,400. Option B is wrong because it reverses the correct entry, increasing Prepaid Insurance instead of decreasing it, which would overstate assets. Option C is wrong because it expenses the entire $9,600 premium, but only 3 of 12 months have expired by year-end; the remaining 9 months are still a prepaid asset. Option D is wrong because it expenses the unexpired portion (9 months: $9,600 × 9/12 = $7,200) rather than the expired portion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="90" customHeight="1">
+      <c r="A199" s="3" t="inlineStr">
+        <is>
+          <t>2. Adjusting Journal Entries / Accounting Cycle</t>
+        </is>
+      </c>
+      <c r="B199" s="3" t="inlineStr">
+        <is>
+          <t>IA-AJE-02</t>
+        </is>
+      </c>
+      <c r="C199" s="3" t="inlineStr">
+        <is>
+          <t>On November 1, Year 1, Stonebridge Company received $18,000 cash from a customer for a 6-month service contract beginning November 1, Year 1. The cash was recorded with a credit to Unearned Revenue. By December 31, Year 1, Stonebridge has completed 2 of the 6 months of service. What is the correct adjusting journal entry on December 31, Year 1?</t>
+        </is>
+      </c>
+      <c r="D199" s="3" t="inlineStr">
+        <is>
+          <t>Debit Unearned Revenue $6,000; Credit Service Revenue $6,000</t>
+        </is>
+      </c>
+      <c r="E199" s="3" t="inlineStr">
+        <is>
+          <t>Debit Unearned Revenue $18,000; Credit Service Revenue $18,000</t>
+        </is>
+      </c>
+      <c r="F199" s="3" t="inlineStr">
+        <is>
+          <t>Debit Cash $18,000; Credit Unearned Revenue $18,000</t>
+        </is>
+      </c>
+      <c r="G199" s="3" t="inlineStr">
+        <is>
+          <t>Debit Service Revenue $6,000; Credit Unearned Revenue $6,000</t>
+        </is>
+      </c>
+      <c r="H199" s="3" t="inlineStr">
+        <is>
+          <t>A. Debit Unearned Revenue $6,000; Credit Service Revenue $6,000</t>
+        </is>
+      </c>
+      <c r="I199" s="3" t="inlineStr">
+        <is>
+          <t>By December 31, Year 1, Stonebridge has earned 2 of 6 months of the contract: $18,000 × 2/6 = $6,000. The adjusting entry transfers the earned portion out of the liability (Unearned Revenue) and into revenue: debit Unearned Revenue $6,000 and credit Service Revenue $6,000. Option B is wrong because it recognizes the full $18,000 as revenue even though only 2 of 6 months of service have been performed; the remaining $12,000 is still unearned. Option C is wrong because it recreates the original entry recording cash received, which has already been recorded and is not an adjusting entry. Option D is wrong because it reverses the correct entry, reducing revenue and increasing the liability, which would understate revenue and overstate Unearned Revenue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="90" customHeight="1">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>11. Payables and Notes Payable</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>IA-PAY-01</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>On January 1, Year 1, Clearfield Company purchases equipment by signing a 3-year noninterest-bearing note with a face amount of $60,000 due at the end of Year 3. The market rate of interest for this type of obligation is 8% per year. What is the initial carrying amount (present value) of the note payable on January 1, Year 1, and what is the total discount recorded at issuance?
+PV of $1 factor (8%, 3 periods): 0.79383</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>Carrying amount: $47,630; Discount on Note Payable: $12,370</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
+        <is>
+          <t>Carrying amount: $60,000; Discount on Note Payable: $0</t>
+        </is>
+      </c>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t>Carrying amount: $54,600; Discount on Note Payable: $5,400</t>
+        </is>
+      </c>
+      <c r="G200" s="2" t="inlineStr">
+        <is>
+          <t>Carrying amount: $47,630; Discount on Note Payable: $47,630</t>
+        </is>
+      </c>
+      <c r="H200" s="2" t="inlineStr">
+        <is>
+          <t>A. Carrying amount: $47,630; Discount on Note Payable: $12,370</t>
+        </is>
+      </c>
+      <c r="I200" s="2" t="inlineStr">
+        <is>
+          <t>A noninterest-bearing note must be recorded at the present value of its future cash flows. The only cash flow is the $60,000 face amount at maturity. PV = $60,000 × 0.79383 = $47,629.80, rounded to $47,630. The discount equals the difference between the face amount and the present value: $60,000 − $47,630 = $12,370. The entry records Equipment and Note Payable at $47,630 and Discount on Note Payable at $12,370. Option B is wrong because it records the note at its face amount, ignoring the required discounting to present value; notes must be recorded at PV when no stated interest is included. Option C is wrong because it deducts only one year of simple interest ($60,000 × 8% × 1 = $4,800 is close to $5,400 but neither equals the correct discount) rather than properly discounting the lump sum to present value. Option D is wrong because the discount equals the difference between face and PV ($12,370), not the present value itself ($47,630).</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="90" customHeight="1">
+      <c r="A201" s="3" t="inlineStr">
+        <is>
+          <t>4. Time Value of Money</t>
+        </is>
+      </c>
+      <c r="B201" s="3" t="inlineStr">
+        <is>
+          <t>IA-TVM-06</t>
+        </is>
+      </c>
+      <c r="C201" s="3" t="inlineStr">
+        <is>
+          <t>A company will pay $10,000 at the BEGINNING of each year for 4 years. The annual discount rate is 8%. The following factors are provided: PV of ordinary annuity of $1 (8%, 4 periods) = 3.31213; PV of annuity due of $1 (8%, 4 periods) = 3.57710; PV of $1 (8%, 4 periods) = 0.73503. What is the present value today of these four payments?</t>
+        </is>
+      </c>
+      <c r="D201" s="3" t="inlineStr">
+        <is>
+          <t>$33,121</t>
+        </is>
+      </c>
+      <c r="E201" s="3" t="inlineStr">
+        <is>
+          <t>$40,000</t>
+        </is>
+      </c>
+      <c r="F201" s="3" t="inlineStr">
+        <is>
+          <t>$35,771</t>
+        </is>
+      </c>
+      <c r="G201" s="3" t="inlineStr">
+        <is>
+          <t>$29,401</t>
+        </is>
+      </c>
+      <c r="H201" s="3" t="inlineStr">
+        <is>
+          <t>C. $35,771</t>
+        </is>
+      </c>
+      <c r="I201" s="3" t="inlineStr">
+        <is>
+          <t>Because payments are made at the BEGINNING of each period, this is an annuity due. The correct factor to apply is the PV of annuity due of $1 (8%, 4 periods) = 3.57710. Correct calculation: $10,000 x 3.57710 = $35,771 (option C). Option A ($33,121) is wrong because it uses the ordinary annuity factor of 3.31213, which applies only when payments occur at the END of each period: $10,000 x 3.31213 = $33,121.30, rounded to $33,121. An ordinary annuity factor understates the present value here because it discounts each payment one period too many. Option B ($40,000) is wrong because it simply sums the four undiscounted payments ($10,000 x 4 = $40,000) and ignores the time value of money entirely. Option D ($29,401) is wrong because it treats the total undiscounted cash flow of $40,000 as a single lump sum received at the end of period 4 and applies the PV of $1 factor: $40,000 x 0.73503 = $29,401.20, rounded to $29,401. This approach incorrectly collapses four separate payments into one and applies a single-sum factor rather than an annuity factor.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I191"/>
+  <autoFilter ref="A1:I201"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Intermediate Accounting Selected MCQs.xlsx
+++ b/Intermediate Accounting Selected MCQs.xlsx
@@ -18271,35 +18271,43 @@
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
+          <t>$20,000</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>$24,000</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>$24,800</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
           <t>$25,250</t>
         </is>
       </c>
-      <c r="E192" s="2" t="inlineStr">
-        <is>
-          <t>$24,800</t>
-        </is>
-      </c>
-      <c r="F192" s="2" t="inlineStr">
-        <is>
-          <t>$20,000</t>
-        </is>
-      </c>
-      <c r="G192" s="2" t="inlineStr">
-        <is>
-          <t>$24,000</t>
-        </is>
-      </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>A. $25,250</t>
+          <t>D. $25,250</t>
         </is>
       </c>
       <c r="I192" s="2" t="inlineStr">
         <is>
-          <t>The future value of a single lump sum is calculated by multiplying the present amount by the FV of $1 factor: $20,000 × 1.26248 = $25,249.60, which rounds to $25,250 (Option A).
-Option B ($24,800) is wrong because it applies simple interest for 4 years rather than compounding: $20,000 × 0.06 × 4 = $4,800 of interest, giving $20,000 + $4,800 = $24,800. This ignores the compounding of interest on interest.
-Option C ($20,000) is wrong because it returns only the original principal with no growth applied—a fundamental conceptual error.
-Option D ($24,000) is wrong because it appears to apply a flat 20% total return (perhaps mistakenly using 5% × 4 years instead of 6% × 4 years under simple interest): $20,000 × 1.20 = $24,000. Neither the rate nor the compounding convention matches the problem.</t>
+          <t>Future Value of a Single Sum
+Explanation
+The future value of a single lump sum is the amount invested today multiplied by the future value of $1 factor for the given rate and number of periods. The factor already reflects compounding, so no separate interest calculation is needed.
+Working
+FV = Present amount x FV of $1 factor (6%, 4 periods)
+FV = $20,000 x 1.26248 = $25,249.60, which rounds to $25,250
+Why Other Options Are Incorrect
+$24,800 - Incorrect. This applies simple interest for four years ($20,000 x 6% x 4 = $4,800) and adds it to the principal. It ignores that interest itself earns interest in each later year.
+$24,000 - Incorrect. This applies a flat 20% total return rather than 6% compounded annually. Neither the rate nor the compounding convention matches the problem.
+$20,000 - Incorrect. This is the original principal with no growth applied at all, which ignores the four years of earnings entirely.
+Summary
+Multiply the amount invested by the future value of $1 factor. The factor does the compounding for you, so $20,000 x 1.26248 = $25,250.</t>
         </is>
       </c>
     </row>
@@ -18322,32 +18330,43 @@
       </c>
       <c r="D193" s="3" t="inlineStr">
         <is>
+          <t>$32,000</t>
+        </is>
+      </c>
+      <c r="E193" s="3" t="inlineStr">
+        <is>
           <t>$34,029</t>
         </is>
       </c>
-      <c r="E193" s="3" t="inlineStr">
+      <c r="F193" s="3" t="inlineStr">
+        <is>
+          <t>$46,000</t>
+        </is>
+      </c>
+      <c r="G193" s="3" t="inlineStr">
         <is>
           <t>$50,000</t>
         </is>
       </c>
-      <c r="F193" s="3" t="inlineStr">
-        <is>
-          <t>$46,000</t>
-        </is>
-      </c>
-      <c r="G193" s="3" t="inlineStr">
-        <is>
-          <t>$32,000</t>
-        </is>
-      </c>
       <c r="H193" s="3" t="inlineStr">
         <is>
-          <t>A. $34,029</t>
+          <t>B. $34,029</t>
         </is>
       </c>
       <c r="I193" s="3" t="inlineStr">
         <is>
-          <t>The present value of a single future amount is the future amount multiplied by the PV of $1 factor. $50,000 × 0.68058 = $34,029. Option B is wrong because it ignores discounting entirely and returns the undiscounted future amount. Option C is wrong because it subtracts only one period of simple interest ($50,000 × 8% × 1 = $4,000), which is not the correct discounting method. Option D is wrong because it uses a rough simple-interest deduction over all five periods ($50,000 − $50,000 × 8% × 5 = $30,000 is closer, but $32,000 reflects an arbitrary approximation that ignores compound discounting).</t>
+          <t>Present Value of a Single Future Amount
+Explanation
+The present value of a single future amount is that amount multiplied by the present value of $1 factor for the given rate and number of periods. Discounting answers what the future receipt is worth in today's dollars.
+Working
+PV = Future amount x PV of $1 factor (8%, 5 periods)
+PV = $50,000 x 0.68058 = $34,029
+Why Other Options Are Incorrect
+$50,000 - Incorrect. This is the undiscounted future amount. Money received in five years is worth less than the same sum today, so some discounting must occur.
+$46,000 - Incorrect. This deducts roughly one period of simple interest rather than discounting across all five periods at the compound rate.
+$32,000 - Incorrect. This approximates the discount with simple interest over five years instead of using the compound present value factor.
+Summary
+Discounting a single future sum takes one factor and one multiplication: $50,000 x 0.68058 = $34,029.</t>
         </is>
       </c>
     </row>
@@ -18369,19 +18388,19 @@
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
+          <t>Stream A has a higher present value because the payments last one additional period.</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>Both streams have the same present value because the total cash paid is identical.</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
           <t>Stream B has a higher present value because each payment is discounted for one fewer period.</t>
         </is>
       </c>
-      <c r="E194" s="2" t="inlineStr">
-        <is>
-          <t>Stream A has a higher present value because the payments last one additional period.</t>
-        </is>
-      </c>
-      <c r="F194" s="2" t="inlineStr">
-        <is>
-          <t>Both streams have the same present value because the total cash paid is identical.</t>
-        </is>
-      </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
           <t>Stream B has a lower present value because beginning-of-period payments carry more risk.</t>
@@ -18389,12 +18408,24 @@
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>A. Stream B has a higher present value because each payment is discounted for one fewer period.</t>
+          <t>C. Stream B has a higher present value because each payment is discounted for one fewer period.</t>
         </is>
       </c>
       <c r="I194" s="2" t="inlineStr">
         <is>
-          <t>An annuity due (Stream B) has a higher present value than an otherwise identical ordinary annuity (Stream A) because each payment arrives one period earlier. Discounting each payment for one fewer period produces a larger present value. The annuity-due PV factor equals the ordinary-annuity PV factor multiplied by (1 + i). Option B is wrong because both streams contain the same number of payments; ordinary annuity payments are not spread over an extra period. Option C is wrong because timing differences cause present values to differ even when total cash is equal. Option D is wrong because receiving money sooner — not later — reduces discounting and increases present value; it has nothing to do with risk.</t>
+          <t>Annuity Due Compared With an Ordinary Annuity
+Explanation
+Stream A is an ordinary annuity, with payments at the end of each year. Stream B is an annuity due, with payments at the beginning of each year. The payments and the rate are identical, so timing is the only difference.
+Each payment in an annuity due arrives one full period earlier, so each is discounted one period less. Less discounting produces a larger present value.
+The Relationship Between the Factors
+PV factor of an annuity due = PV factor of an ordinary annuity x (1 + i)
+Since (1 + i) is greater than 1 for any positive rate, the annuity due factor is always the larger of the two.
+Why Other Options Are Incorrect
+Stream A has a higher present value - Incorrect. Both streams contain six payments. An ordinary annuity does not run an extra period; its payments simply fall later within the same six years.
+Both streams have the same present value - Incorrect. The undiscounted totals are equal at $30,000, but present value depends on when each payment arrives, not just how much is paid.
+Stream B has a lower present value - Incorrect. Receiving money earlier increases present value. Timing of payment within an annuity is not a risk adjustment.
+Summary
+Same payments and same rate, but earlier timing: the annuity due has the higher present value because every payment is discounted for one period less.</t>
         </is>
       </c>
     </row>
@@ -18417,19 +18448,19 @@
       </c>
       <c r="D195" s="3" t="inlineStr">
         <is>
+          <t>$40,000</t>
+        </is>
+      </c>
+      <c r="E195" s="3" t="inlineStr">
+        <is>
+          <t>$42,000</t>
+        </is>
+      </c>
+      <c r="F195" s="3" t="inlineStr">
+        <is>
           <t>$44,205</t>
         </is>
       </c>
-      <c r="E195" s="3" t="inlineStr">
-        <is>
-          <t>$40,000</t>
-        </is>
-      </c>
-      <c r="F195" s="3" t="inlineStr">
-        <is>
-          <t>$42,000</t>
-        </is>
-      </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
           <t>$46,000</t>
@@ -18437,12 +18468,23 @@
       </c>
       <c r="H195" s="3" t="inlineStr">
         <is>
-          <t>A. $44,205</t>
+          <t>C. $44,205</t>
         </is>
       </c>
       <c r="I195" s="3" t="inlineStr">
         <is>
-          <t>The future value of an ordinary annuity equals the periodic payment multiplied by the FV of ordinary annuity factor. $8,000 × 5.52563 = $44,205.04, which rounds to $44,205. Option B is wrong because it sums only the deposits without adding any interest ($8,000 × 5 = $40,000). Option C is wrong because it adds a rough, understated interest estimate to the total deposits. Option D is wrong because it overstates the interest by applying the full 5% rate to all deposits for all five years simultaneously, ignoring that early deposits earn interest for more years than later deposits.</t>
+          <t>Future Value of an Ordinary Annuity
+Explanation
+Equal deposits made at the end of each period form an ordinary annuity. The accumulated balance is the periodic deposit multiplied by the future value of an ordinary annuity factor, which accounts for each deposit earning interest for a different length of time.
+Working
+FV = Periodic deposit x FV of ordinary annuity factor (5%, 5 periods)
+FV = $8,000 x 5.52563 = $44,205.04, which rounds to $44,205
+Why Other Options Are Incorrect
+$40,000 - Incorrect. This is the sum of the five deposits ($8,000 x 5) with no interest at all, which ignores the fund's earnings.
+$46,000 - Incorrect. This overstates the interest by crediting every deposit with a full five years of earnings. The final deposit earns nothing, because it is made on the last day.
+$42,000 - Incorrect. This adds a rough interest estimate to the deposits rather than applying the annuity factor.
+Summary
+The annuity factor handles the staggered timing of each deposit: $8,000 x 5.52563 = $44,205.</t>
         </is>
       </c>
     </row>
@@ -18465,32 +18507,43 @@
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
+          <t>$62,000</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
           <t>$67,289</t>
         </is>
       </c>
-      <c r="E196" s="2" t="inlineStr">
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>$73,500</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="inlineStr">
         <is>
           <t>$90,000</t>
         </is>
       </c>
-      <c r="F196" s="2" t="inlineStr">
-        <is>
-          <t>$73,500</t>
-        </is>
-      </c>
-      <c r="G196" s="2" t="inlineStr">
-        <is>
-          <t>$62,000</t>
-        </is>
-      </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>A. $67,289</t>
+          <t>B. $67,289</t>
         </is>
       </c>
       <c r="I196" s="2" t="inlineStr">
         <is>
-          <t>The present value of an ordinary annuity equals the periodic payment multiplied by the PV of ordinary annuity factor. $15,000 × 4.48592 = $67,288.80, which rounds to $67,289. Option B is wrong because it sums the undiscounted payments ($15,000 × 6 = $90,000) without applying any discounting. Option C is wrong because it applies an incorrect, lower annuity factor, understating the number of periods or the factor. Option D is wrong because it uses a PV of a single-sum factor instead of an annuity factor, treating the entire $90,000 as one lump sum discounted at an arbitrary rate.</t>
+          <t>Present Value of an Ordinary Annuity
+Explanation
+A settlement paying a fixed amount at the end of each year is an ordinary annuity. Its value today is the periodic payment multiplied by the present value of an ordinary annuity factor for the given rate and number of payments.
+Working
+PV = Periodic payment x PV of ordinary annuity factor (9%, 6 periods)
+PV = $15,000 x 4.48592 = $67,288.80, which rounds to $67,289
+Why Other Options Are Incorrect
+$90,000 - Incorrect. This is the sum of the six undiscounted payments ($15,000 x 6). It ignores that money arriving over six years is worth less than money in hand.
+$73,500 - Incorrect. This applies an annuity factor that is too high for six periods at 9%, understating the discount.
+$62,000 - Incorrect. This treats the total as a single lump sum discounted once, rather than discounting six separate payments each for its own number of periods.
+Summary
+Six equal year-end payments discounted at 9%: $15,000 x 4.48592 = $67,289.</t>
         </is>
       </c>
     </row>
@@ -18524,14 +18577,14 @@
       </c>
       <c r="F197" s="3" t="inlineStr">
         <is>
+          <t>$36,000</t>
+        </is>
+      </c>
+      <c r="G197" s="3" t="inlineStr">
+        <is>
           <t>$40,000</t>
         </is>
       </c>
-      <c r="G197" s="3" t="inlineStr">
-        <is>
-          <t>$36,000</t>
-        </is>
-      </c>
       <c r="H197" s="3" t="inlineStr">
         <is>
           <t>A. $29,849</t>
@@ -18539,7 +18592,22 @@
       </c>
       <c r="I197" s="3" t="inlineStr">
         <is>
-          <t>When compounding is semiannual, the periodic rate is the annual rate divided by 2 (10% / 2 = 5%) and the number of periods is years multiplied by 2 (3 × 2 = 6 periods). The correct PV factor is therefore the one at 5% for 6 periods: 0.74622. $40,000 × 0.74622 = $29,848.80, which rounds to $29,849. Option B is wrong because it uses the annual factor (10%, 3 periods: 0.75131), failing to adjust for semiannual compounding; $40,000 × 0.75131 = $30,052. Option C is wrong because it deposits the full future amount today with no discounting. Option D is wrong because it deducts only one period of simple interest ($40,000 × 10% = $4,000) from the future amount, which does not reflect proper discounting.</t>
+          <t>Discounting With Semiannual Compounding
+Explanation
+When compounding is more frequent than annually, the rate and the number of periods must both be converted before any factor is applied. This is the single most common error in time value questions.
+Converting the Rate and the Periods
+Periodic rate = annual rate divided by the number of compounding periods per year: 10% / 2 = 5%
+Number of periods = years multiplied by compounding periods per year: 3 x 2 = 6
+The correct factor is therefore the one at 5% for 6 periods, which is 0.74622.
+Working
+Deposit required = Future amount x PV of $1 factor (5%, 6 periods)
+Deposit required = $40,000 x 0.74622 = $29,848.80, which rounds to $29,849
+Why Other Options Are Incorrect
+$30,052 - Incorrect. This uses the annual factor at 10% for 3 periods (0.75131), leaving the rate and periods unconverted. More frequent compounding means a smaller deposit is needed, not a larger one.
+$40,000 - Incorrect. This deposits the full future amount today, applying no discounting at all.
+$36,000 - Incorrect. This deducts a single period of simple interest from the future amount rather than discounting it over six compounding periods.
+Summary
+Halve the rate and double the periods before reaching for a factor: $40,000 x 0.74622 = $29,849.</t>
         </is>
       </c>
     </row>
@@ -18561,32 +18629,45 @@
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
+          <t>Debit Insurance Expense $9,600; Credit Prepaid Insurance $9,600</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>Debit Insurance Expense $7,200; Credit Prepaid Insurance $7,200</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>Debit Prepaid Insurance $2,400; Credit Insurance Expense $2,400</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="inlineStr">
+        <is>
           <t>Debit Insurance Expense $2,400; Credit Prepaid Insurance $2,400</t>
         </is>
       </c>
-      <c r="E198" s="2" t="inlineStr">
-        <is>
-          <t>Debit Prepaid Insurance $2,400; Credit Insurance Expense $2,400</t>
-        </is>
-      </c>
-      <c r="F198" s="2" t="inlineStr">
-        <is>
-          <t>Debit Insurance Expense $9,600; Credit Prepaid Insurance $9,600</t>
-        </is>
-      </c>
-      <c r="G198" s="2" t="inlineStr">
-        <is>
-          <t>Debit Insurance Expense $7,200; Credit Prepaid Insurance $7,200</t>
-        </is>
-      </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
-          <t>A. Debit Insurance Expense $2,400; Credit Prepaid Insurance $2,400</t>
+          <t>D. Debit Insurance Expense $2,400; Credit Prepaid Insurance $2,400</t>
         </is>
       </c>
       <c r="I198" s="2" t="inlineStr">
         <is>
-          <t>By December 31, Year 1, three months of the policy have elapsed (October, November, December). The expired portion is $9,600 × 3/12 = $2,400. The adjusting entry records the expense for the expired coverage and reduces Prepaid Insurance accordingly: debit Insurance Expense $2,400 and credit Prepaid Insurance $2,400. Option B is wrong because it reverses the correct entry, increasing Prepaid Insurance instead of decreasing it, which would overstate assets. Option C is wrong because it expenses the entire $9,600 premium, but only 3 of 12 months have expired by year-end; the remaining 9 months are still a prepaid asset. Option D is wrong because it expenses the unexpired portion (9 months: $9,600 × 9/12 = $7,200) rather than the expired portion.</t>
+          <t>Adjusting a Prepaid Insurance Balance
+Explanation
+The full premium was recorded as an asset when paid. At year-end the adjusting entry moves the portion of coverage that has been used out of the asset and into expense, leaving the unused coverage on the balance sheet.
+Working
+Monthly cost = $9,600 / 12 months = $800 per month
+Months expired from October 1 through December 31 = 3
+Expired portion = $800 x 3 = $2,400
+The entry debits Insurance Expense $2,400 and credits Prepaid Insurance $2,400, leaving $7,200 of prepaid coverage for the nine months that fall in Year 2.
+Why Other Options Are Incorrect
+Expensing the full $9,600 - Incorrect. Only three of the twelve months have expired by December 31. The remaining nine months are still an asset.
+Expensing $7,200 - Incorrect. This expenses the unexpired portion and leaves the used portion on the balance sheet, exactly reversing the split.
+Debiting Prepaid and crediting Expense - Incorrect. This runs the entry backwards, increasing the asset and overstating both assets and net income.
+Summary
+Expense what has been used, not what remains: three months of a twelve-month policy is $2,400.</t>
         </is>
       </c>
     </row>
@@ -18608,19 +18689,19 @@
       </c>
       <c r="D199" s="3" t="inlineStr">
         <is>
+          <t>Debit Cash $18,000; Credit Unearned Revenue $18,000</t>
+        </is>
+      </c>
+      <c r="E199" s="3" t="inlineStr">
+        <is>
           <t>Debit Unearned Revenue $6,000; Credit Service Revenue $6,000</t>
         </is>
       </c>
-      <c r="E199" s="3" t="inlineStr">
+      <c r="F199" s="3" t="inlineStr">
         <is>
           <t>Debit Unearned Revenue $18,000; Credit Service Revenue $18,000</t>
         </is>
       </c>
-      <c r="F199" s="3" t="inlineStr">
-        <is>
-          <t>Debit Cash $18,000; Credit Unearned Revenue $18,000</t>
-        </is>
-      </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
           <t>Debit Service Revenue $6,000; Credit Unearned Revenue $6,000</t>
@@ -18628,12 +18709,25 @@
       </c>
       <c r="H199" s="3" t="inlineStr">
         <is>
-          <t>A. Debit Unearned Revenue $6,000; Credit Service Revenue $6,000</t>
+          <t>B. Debit Unearned Revenue $6,000; Credit Service Revenue $6,000</t>
         </is>
       </c>
       <c r="I199" s="3" t="inlineStr">
         <is>
-          <t>By December 31, Year 1, Stonebridge has earned 2 of 6 months of the contract: $18,000 × 2/6 = $6,000. The adjusting entry transfers the earned portion out of the liability (Unearned Revenue) and into revenue: debit Unearned Revenue $6,000 and credit Service Revenue $6,000. Option B is wrong because it recognizes the full $18,000 as revenue even though only 2 of 6 months of service have been performed; the remaining $12,000 is still unearned. Option C is wrong because it recreates the original entry recording cash received, which has already been recorded and is not an adjusting entry. Option D is wrong because it reverses the correct entry, reducing revenue and increasing the liability, which would understate revenue and overstate Unearned Revenue.</t>
+          <t>Adjusting an Unearned Revenue Balance
+Explanation
+Cash collected before a service is performed creates a liability, not revenue. At year-end the adjusting entry recognizes only the portion that has actually been earned and leaves the rest in the liability.
+Working
+Monthly revenue = $18,000 / 6 months = $3,000 per month
+Months performed from November 1 through December 31 = 2
+Earned portion = $3,000 x 2 = $6,000
+The entry debits Unearned Revenue $6,000 and credits Service Revenue $6,000, leaving $12,000 of unearned revenue for the four months still to be performed.
+Why Other Options Are Incorrect
+Recognizing the full $18,000 - Incorrect. Only two of the six months of service have been performed. The remaining $12,000 has not been earned.
+Debiting Cash and crediting Unearned Revenue - Incorrect. This repeats the original entry for the cash receipt, which was already recorded on November 1. It is not an adjusting entry.
+Debiting Service Revenue and crediting Unearned Revenue - Incorrect. This runs the entry backwards, reducing revenue and increasing the liability.
+Summary
+Recognize revenue as the service is performed: two of six months earned is $6,000.</t>
         </is>
       </c>
     </row>
@@ -18656,19 +18750,19 @@
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
+          <t>Carrying amount: $60,000; Discount on Note Payable: $0</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
+        <is>
+          <t>Carrying amount: $54,600; Discount on Note Payable: $5,400</t>
+        </is>
+      </c>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
           <t>Carrying amount: $47,630; Discount on Note Payable: $12,370</t>
         </is>
       </c>
-      <c r="E200" s="2" t="inlineStr">
-        <is>
-          <t>Carrying amount: $60,000; Discount on Note Payable: $0</t>
-        </is>
-      </c>
-      <c r="F200" s="2" t="inlineStr">
-        <is>
-          <t>Carrying amount: $54,600; Discount on Note Payable: $5,400</t>
-        </is>
-      </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
           <t>Carrying amount: $47,630; Discount on Note Payable: $47,630</t>
@@ -18676,12 +18770,26 @@
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
-          <t>A. Carrying amount: $47,630; Discount on Note Payable: $12,370</t>
+          <t>C. Carrying amount: $47,630; Discount on Note Payable: $12,370</t>
         </is>
       </c>
       <c r="I200" s="2" t="inlineStr">
         <is>
-          <t>A noninterest-bearing note must be recorded at the present value of its future cash flows. The only cash flow is the $60,000 face amount at maturity. PV = $60,000 × 0.79383 = $47,629.80, rounded to $47,630. The discount equals the difference between the face amount and the present value: $60,000 − $47,630 = $12,370. The entry records Equipment and Note Payable at $47,630 and Discount on Note Payable at $12,370. Option B is wrong because it records the note at its face amount, ignoring the required discounting to present value; notes must be recorded at PV when no stated interest is included. Option C is wrong because it deducts only one year of simple interest ($60,000 × 8% × 1 = $4,800 is close to $5,400 but neither equals the correct discount) rather than properly discounting the lump sum to present value. Option D is wrong because the discount equals the difference between face and PV ($12,370), not the present value itself ($47,630).</t>
+          <t>Recording a Noninterest-Bearing Note at Present Value
+Explanation
+A note described as noninterest-bearing still carries interest; the interest is simply bundled into the face amount rather than stated separately. The note is recorded at the present value of its future cash flows, and the difference between face and present value is set up as a discount that is amortized to interest expense over the term.
+Working
+The only cash flow is the $60,000 face amount due at the end of Year 3.
+Present value = $60,000 x PV of $1 factor (8%, 3 periods)
+Present value = $60,000 x 0.79383 = $47,629.80, which rounds to $47,630
+Discount = Face amount less present value = $60,000 - $47,630 = $12,370
+Equipment and the note are recorded at $47,630, with the $12,370 discount amortized to interest expense across the three years.
+Why Other Options Are Incorrect
+Carrying amount $60,000 with no discount - Incorrect. Recording the note at face ignores the required discounting and would overstate both the equipment and the liability.
+Carrying amount $54,600 with a $5,400 discount - Incorrect. This deducts roughly one year of interest rather than discounting the lump sum across all three years.
+A discount of $47,630 - Incorrect. This mistakes the present value for the discount. The discount is the difference between face and present value, not the present value itself.
+Summary
+Record the note at the present value of what will be paid: $47,630, with the $12,370 difference carried as a discount and amortized to interest expense.</t>
         </is>
       </c>
     </row>
@@ -18703,24 +18811,24 @@
       </c>
       <c r="D201" s="3" t="inlineStr">
         <is>
+          <t>$29,401</t>
+        </is>
+      </c>
+      <c r="E201" s="3" t="inlineStr">
+        <is>
           <t>$33,121</t>
         </is>
       </c>
-      <c r="E201" s="3" t="inlineStr">
+      <c r="F201" s="3" t="inlineStr">
+        <is>
+          <t>$35,771</t>
+        </is>
+      </c>
+      <c r="G201" s="3" t="inlineStr">
         <is>
           <t>$40,000</t>
         </is>
       </c>
-      <c r="F201" s="3" t="inlineStr">
-        <is>
-          <t>$35,771</t>
-        </is>
-      </c>
-      <c r="G201" s="3" t="inlineStr">
-        <is>
-          <t>$29,401</t>
-        </is>
-      </c>
       <c r="H201" s="3" t="inlineStr">
         <is>
           <t>C. $35,771</t>
@@ -18728,7 +18836,18 @@
       </c>
       <c r="I201" s="3" t="inlineStr">
         <is>
-          <t>Because payments are made at the BEGINNING of each period, this is an annuity due. The correct factor to apply is the PV of annuity due of $1 (8%, 4 periods) = 3.57710. Correct calculation: $10,000 x 3.57710 = $35,771 (option C). Option A ($33,121) is wrong because it uses the ordinary annuity factor of 3.31213, which applies only when payments occur at the END of each period: $10,000 x 3.31213 = $33,121.30, rounded to $33,121. An ordinary annuity factor understates the present value here because it discounts each payment one period too many. Option B ($40,000) is wrong because it simply sums the four undiscounted payments ($10,000 x 4 = $40,000) and ignores the time value of money entirely. Option D ($29,401) is wrong because it treats the total undiscounted cash flow of $40,000 as a single lump sum received at the end of period 4 and applies the PV of $1 factor: $40,000 x 0.73503 = $29,401.20, rounded to $29,401. This approach incorrectly collapses four separate payments into one and applies a single-sum factor rather than an annuity factor.</t>
+          <t>Present Value of an Annuity Due
+Explanation
+Payments made at the beginning of each period form an annuity due, so the annuity due factor is the one to apply. Each payment is discounted one period less than it would be under an ordinary annuity.
+Working
+PV = Periodic payment x PV of annuity due factor (8%, 4 periods)
+PV = $10,000 x 3.57710 = $35,771
+Why Other Options Are Incorrect
+$33,121 - Incorrect. This uses the ordinary annuity factor of 3.31213, which applies only when payments fall at the end of each period. It discounts every payment one period too many.
+$40,000 - Incorrect. This sums the four undiscounted payments and ignores the time value of money entirely.
+$29,401 - Incorrect. This collapses all four payments into a single $40,000 lump sum at the end of period 4 and applies the PV of $1 factor, which both mistimes the payments and uses the wrong kind of factor.
+Summary
+Beginning-of-period payments call for the annuity due factor: $10,000 x 3.57710 = $35,771.</t>
         </is>
       </c>
     </row>

--- a/Intermediate Accounting Selected MCQs.xlsx
+++ b/Intermediate Accounting Selected MCQs.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I201"/>
+  <dimension ref="A1:I221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -18732,6 +18732,1199 @@
         </is>
       </c>
     </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>21. Pensions and Postretirement Benefits</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>IA-PEN-01</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Which of the following is NOT a component of net periodic pension cost?</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Interest cost on the projected benefit obligation</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Expected return on the plan's assets for the period</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Amortization of prior service cost from a plan amendment</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Employer contributions to the plan</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>D. Employer contributions to the plan</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Components of Net Periodic Pension Cost
+Explanation
+Net periodic pension cost is an expense measure. It is built from the actuarial movements in the obligation and the plan assets, not from the cash the employer puts into the fund.
+The components are service cost, interest cost, expected return on plan assets, amortization of prior service cost, and amortization of net gain or loss.
+Contributions Are Funding, Not Expense
+A contribution moves cash from the employer to the trust. It increases plan assets and reduces any accrued pension liability, but it never appears in the expense calculation. An employer can contribute nothing in a year and still record a large pension cost, or contribute heavily and still record a small one.
+Why Other Options Are Incorrect
+Interest cost - Incorrect. This is a component. It is the growth in the obligation from the passage of time, measured as the beginning projected benefit obligation times the discount rate.
+Expected return on plan assets - Incorrect. This is a component, and it reduces the cost rather than adding to it.
+Amortization of prior service cost - Incorrect. This is a component. It brings the cost of a plan amendment into expense over the remaining service period.
+Summary
+Service cost, interest cost, expected return, and the two amortizations make up the expense. Contributions fund the plan and are not part of it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>21. Pensions and Postretirement Benefits</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>IA-PEN-02</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Ridgeline Corp. reports the following for the current year:
+Service cost: $250,000
+Interest cost: $180,000
+Expected return on plan assets: $200,000
+Amortization of prior service cost: $30,000
+What is Ridgeline's net periodic pension cost for the year?</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>$220,000</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>$260,000</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>$460,000</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>$660,000</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>B. $260,000</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>Computing Net Periodic Pension Cost
+Explanation
+Net periodic pension cost adds the components that increase the obligation and subtracts the one that offsets it. Only the expected return on plan assets is subtracted.
+Working
+Service cost: $250,000
+Plus interest cost: $180,000
+Less expected return on plan assets: ($200,000)
+Plus amortization of prior service cost: $30,000
+Net periodic pension cost = $250,000 + $180,000 - $200,000 + $30,000 = $260,000
+Why Other Options Are Incorrect
+$660,000 - Incorrect. This adds every component, treating the expected return as a cost rather than an offset. The return earned inside the plan reduces what the employer must bear.
+$460,000 - Incorrect. This omits the expected return entirely instead of subtracting it.
+$220,000 - Incorrect. This subtracts the amortization of prior service cost. Amortization increases the expense, because it brings a past plan amendment into income over the remaining service period.
+Summary
+Add service cost, interest cost, and the amortizations; subtract the expected return. Here that is $260,000.</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>21. Pensions and Postretirement Benefits</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>IA-PEN-03</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Calder Industries reports a projected benefit obligation of $1,500,000 at January 1. During the year, service cost is $200,000, the discount rate is 8%, and benefits of $90,000 are paid to retirees. There are no actuarial gains or losses.
+What is the projected benefit obligation at December 31?</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>$1,610,000</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>$1,700,000</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>$1,730,000</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>$1,820,000</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>C. $1,730,000</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>Rolling Forward the Projected Benefit Obligation
+Explanation
+The obligation grows for the benefits employees earned this year and for the passage of time, and shrinks as benefits are actually paid out.
+Interest cost is the beginning obligation multiplied by the discount rate, not the ending obligation.
+Working
+Beginning projected benefit obligation: $1,500,000
+Plus service cost: $200,000
+Plus interest cost ($1,500,000 x 8%): $120,000
+Less benefits paid: ($90,000)
+Ending projected benefit obligation = $1,730,000
+Why Other Options Are Incorrect
+$1,820,000 - Incorrect. This omits the benefits paid. Paying a retiree settles part of the promise and reduces the obligation.
+$1,700,000 - Incorrect. This omits interest cost. The obligation is a discounted amount, so it grows each year simply because settlement is one year closer.
+$1,610,000 - Incorrect. This omits service cost, which is the present value of the benefits employees earned by working this year.
+Summary
+Beginning obligation, plus service cost, plus interest on the beginning balance, less benefits paid: $1,730,000.</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>21. Pensions and Postretirement Benefits</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>IA-PEN-04</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Marwick Co. reports plan assets with a fair value of $1,200,000 at January 1. During the year the plan earns an actual return of $110,000, the employer contributes $250,000, and benefits of $90,000 are paid to retirees.
+What is the fair value of plan assets at December 31?</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>$1,220,000</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>$1,470,000</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>$1,560,000</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>$1,650,000</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>B. $1,470,000</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>Rolling Forward Plan Assets
+Explanation
+Plan assets are a fund held by a trustee. The roll-forward tracks cash and investment performance: what the fund earns and receives increases it, and what it pays out decreases it.
+The actual return is used here, not the expected return. Expected return belongs to the expense calculation; the asset balance reflects what the fund really earned.
+Working
+Beginning plan assets: $1,200,000
+Plus actual return on plan assets: $110,000
+Plus employer contributions: $250,000
+Less benefits paid: ($90,000)
+Ending plan assets = $1,470,000
+Why Other Options Are Incorrect
+$1,650,000 - Incorrect. This adds the benefits paid instead of subtracting them. Benefits are paid out of the fund, so they reduce it.
+$1,560,000 - Incorrect. This omits the benefits paid.
+$1,220,000 - Incorrect. This omits the employer contribution, which is the main way the fund is built up.
+Summary
+Beginning assets, plus actual return, plus contributions, less benefits paid: $1,470,000. Benefits paid reduce both the obligation and the plan assets by the same amount.</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>21. Pensions and Postretirement Benefits</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>IA-PEN-05</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>At December 31, Brightwater Inc. reports a projected benefit obligation of $3,200,000 and plan assets with a fair value of $2,750,000. How should Brightwater report its pension plan on the December 31 balance sheet?</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>A net pension liability of $450,000</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>A net pension asset of $450,000</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>A liability of $3,200,000 and an asset of $2,750,000, reported separately</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>No amount on the balance sheet; the funded status is disclosed in the notes</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>A. A net pension liability of $450,000</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>Reporting Funded Status on the Balance Sheet
+Explanation
+The balance sheet reports the funded status of the plan: plan assets at fair value less the projected benefit obligation. A single net amount is reported, not the two gross balances.
+Working
+Plan assets at fair value: $2,750,000
+Less projected benefit obligation: ($3,200,000)
+Funded status = ($450,000)
+The obligation exceeds the assets, so the plan is underfunded and the net amount is a liability of $450,000. Had assets exceeded the obligation, the overfunded amount would be reported as a noncurrent asset.
+Why Other Options Are Incorrect
+A net pension asset of $450,000 - Incorrect. The direction is reversed. An asset arises only when plan assets exceed the obligation.
+Gross liability and asset reported separately - Incorrect. Plan assets are not the employer's own assets to report gross; the two are netted into a single funded status figure.
+Disclosure only - Incorrect. Funded status has been recognized on the balance sheet, not merely disclosed, since the standard was amended to require it.
+Summary
+Report the net funded status. Assets of $2,750,000 against an obligation of $3,200,000 is a $450,000 net pension liability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>21. Pensions and Postretirement Benefits</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>IA-PEN-06</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Halstead Corp.'s plan assets have a fair value of $2,000,000 at January 1. The expected long-term rate of return is 7%, and the plan's actual return for the year is $190,000.
+What amount is included in net periodic pension cost as a reduction for the return on plan assets?</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>$50,000</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>$140,000</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>$190,000</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>$330,000</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>B. $140,000</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>Expected Return, Not Actual Return, Enters Pension Cost
+Explanation
+Pension expense uses the expected return on plan assets. Using the actual return would push market volatility straight into earnings, which is exactly what the expected-return convention is designed to prevent.
+Working
+Expected return = Beginning plan assets x expected long-term rate
+Expected return = $2,000,000 x 7% = $140,000
+This reduces net periodic pension cost by $140,000.
+What Happens to the Difference
+The actual return of $190,000 exceeded the expected $140,000 by $50,000. That $50,000 is an actuarial gain. It does not adjust this year's expense directly; it goes to other comprehensive income and may reach expense later through corridor amortization.
+Why Other Options Are Incorrect
+$190,000 - Incorrect. This is the actual return. It is used to roll forward plan assets, not to compute the expense.
+$50,000 - Incorrect. This is the gain, the difference between actual and expected, rather than the return component itself.
+$330,000 - Incorrect. This adds the expected and actual returns together, double counting a single year's earnings.
+Summary
+The expense uses expected return of $140,000. The $50,000 excess is an actuarial gain routed through other comprehensive income.</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>21. Pensions and Postretirement Benefits</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>IA-PEN-07</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Fairmont Company amends its defined benefit pension plan, increasing benefits for services employees have already rendered. How is the resulting prior service cost accounted for at the date of the amendment?</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Recognized immediately in full as pension expense in the year of the amendment</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Recorded as a prepaid pension asset and amortized over the life of the plan</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Recognized in other comprehensive income, then amortized to pension expense</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Disclosed in the notes, with no amount recognized until the benefits are actually paid</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>C. Recognized in other comprehensive income, then amortized to pension expense</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>Accounting for a Plan Amendment
+Explanation
+Amending a plan to improve benefits for past service increases the projected benefit obligation immediately. The employer grants that improvement expecting future benefit from the workforce, so the cost is not charged to income all at once.
+At the amendment date the increase in the obligation is recognized in other comprehensive income as prior service cost. It is then amortized out of accumulated other comprehensive income into pension expense over the remaining service period of the employees who will benefit from it.
+Why the Two-Step Treatment
+The obligation is recognized at once, so the balance sheet reflects the full promise. Income is charged gradually, so the expense follows the service period the amendment was meant to reward. This is why prior service cost appears both in accumulated other comprehensive income and, year by year, as a component of pension cost.
+Why Other Options Are Incorrect
+Recognized immediately in full as expense - Incorrect. Immediate expensing would charge income with a cost intended to benefit several future periods.
+Recorded as a prepaid asset - Incorrect. The amendment creates an obligation, not an asset. Nothing has been prepaid.
+Disclosed only - Incorrect. The increase in the obligation is recognized when the plan is amended, not deferred until benefits are paid.
+Summary
+Prior service cost goes to other comprehensive income at the amendment date and reaches pension expense through amortization over the remaining service period.</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>21. Pensions and Postretirement Benefits</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>IA-PEN-08</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Lindqvist Corp. reports an unrecognized net loss of $480,000 in accumulated other comprehensive income at the beginning of the year. At the same date the projected benefit obligation is $3,000,000 and plan assets have a fair value of $2,600,000. The average remaining service period of active employees is 10 years.
+Using the corridor approach, what amount of the net loss is amortized into pension cost this year?</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>$18,000</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>$30,000</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>$48,000</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>B. $18,000</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>Corridor Amortization of a Net Loss
+Explanation
+Actuarial gains and losses arise constantly as assumptions are revised and returns differ from expectations. The corridor lets small ones accumulate without touching expense, and amortizes only the part that has grown large relative to the plan.
+Step 1: Measure the Corridor
+The corridor is 10% of the greater of the projected benefit obligation or the fair value of plan assets.
+Greater of $3,000,000 and $2,600,000 = $3,000,000
+Corridor = 10% x $3,000,000 = $300,000
+Step 2: Find the Excess
+Net loss of $480,000 less the $300,000 corridor = $180,000 outside the corridor
+Step 3: Amortize the Excess
+Amortization = $180,000 / 10 years = $18,000
+Only the excess is amortized, and only over the average remaining service period.
+Why Other Options Are Incorrect
+$48,000 - Incorrect. This amortizes the entire $480,000 net loss over 10 years, ignoring the corridor. The amount inside the corridor stays in accumulated other comprehensive income.
+$30,000 - Incorrect. This amortizes the corridor itself rather than the excess above it.
+$0 - Incorrect. Nothing would be amortized only if the net loss were within the corridor. Here it exceeds $300,000.
+Summary
+Corridor of $300,000, excess of $180,000, spread over 10 years: $18,000 amortized into pension cost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>21. Pensions and Postretirement Benefits</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>IA-PEN-09</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Which statement correctly describes a defined contribution plan?</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>The employer owes only its agreed contribution, and the employee bears the investment risk.</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>The employer promises a specified benefit at retirement and bears the investment risk on plan assets.</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>The employer must measure and report a projected benefit obligation for the plan.</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Annual expense is determined by actuarial assumptions about mortality and discount rates.</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>A. The employer owes only its agreed contribution, and the employee bears the investment risk.</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>Defined Contribution Compared With Defined Benefit
+Explanation
+The distinction is about who carries the investment risk, and it drives everything else about the accounting.
+Under a defined contribution plan the employer promises only to pay in an agreed amount. Once the contribution is made the employer's obligation is discharged. Whatever the account grows to is what the employee receives, so the employee carries the investment risk.
+Under a defined benefit plan the employer promises a specified benefit at retirement. If plan investments underperform, the employer must make up the shortfall, so the employer carries the risk.
+What This Means for the Accounting
+A defined contribution plan needs no actuary. Expense equals the contribution owed for the period, and there is no projected benefit obligation, no plan asset roll-forward, and no corridor. The elaborate machinery of pension accounting exists only because a defined benefit promise has to be measured.
+Why Other Options Are Incorrect
+The employer promises a specified benefit and bears investment risk - Incorrect. That describes a defined benefit plan.
+The employer reports a projected benefit obligation - Incorrect. A projected benefit obligation measures a promised future benefit, which a defined contribution plan does not make.
+Expense is determined by actuarial assumptions - Incorrect. Actuarial assumptions are needed for defined benefit plans. Defined contribution expense is simply the agreed contribution.
+Summary
+Defined contribution: the employer owes a contribution and the employee bears investment risk. Defined benefit: the employer owes a benefit and bears the risk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>21. Pensions and Postretirement Benefits</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>IA-PEN-10</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Under current U.S. GAAP, how are the components of net periodic pension cost presented in the income statement of an employer that reports a subtotal for income from operations?</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>All components are combined into a single net amount reported within operating expenses.</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>All components are reported in other comprehensive income rather than net income.</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Service cost is reported outside operations, and the remaining components are reported within operating expenses.</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Service cost sits with employee compensation; the other components are presented separately, outside operations.</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>D. Service cost sits with employee compensation; the other components are presented separately, outside operations.</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Where the Components Are Presented
+Explanation
+The components of pension cost are not alike, and the presentation requirements now reflect that.
+Service cost is the cost of benefits employees earned by working this period. It is compensation, so it is reported in the same line items as other employee compensation, within income from operations.
+The remaining components, which are interest cost, expected return on plan assets, and the amortizations, are financing and actuarial in nature. They are presented separately from service cost and outside any subtotal of income from operations.
+Why the Split Matters
+Before this requirement a single net figure mixed compensation with investment performance, so a strong year in the plan's portfolio could flatter operating income. Separating the components keeps operating results tied to operations.
+Why Other Options Are Incorrect
+All components combined in operating expenses - Incorrect. This is the treatment the current requirement replaced, and it lets plan investment returns move operating income.
+All components in other comprehensive income - Incorrect. Pension cost is an expense in net income. Other comprehensive income holds unrecognized gains and losses and prior service cost until they are amortized.
+Service cost outside operations with the rest inside - Incorrect. This reverses the treatment. Service cost is the component that genuinely is compensation.
+Summary
+Service cost sits with compensation inside operations. Interest, expected return, and amortizations are presented separately, below that subtotal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>22. Stock-Based Compensation</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>IA-SBC-01</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Under U.S. GAAP, compensation cost for an equity-classified share-based payment award is measured based on:</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>The fair value of the award at the grant date</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>The intrinsic value of the award at the exercise date</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>The fair value of the award remeasured at each reporting date until exercise</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>The exercise price stated in the award agreement</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>A. The fair value of the award at the grant date</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>Measuring an Equity-Classified Award
+Explanation
+An equity-classified award is measured once, at the grant date, using the fair value of the award itself. That measurement is then fixed. The total compensation cost is the grant-date fair value multiplied by the number of awards expected to vest, and it is recognized over the service period.
+Fixing the measurement at grant date is what separates equity awards from liability awards. Because the company will settle in its own shares, it takes on no further obligation as the share price moves, so later price changes do not alter the cost.
+Why Other Options Are Incorrect
+Intrinsic value at the exercise date - Incorrect. Intrinsic value ignores the time value that makes an option valuable when granted, and exercise-date measurement would leave the cost unknown for years.
+Fair value remeasured each reporting date - Incorrect. This is the treatment for liability-classified awards, such as cash-settled stock appreciation rights. Equity awards are not remeasured.
+The exercise price - Incorrect. The exercise price is an input to valuing the option, not the cost. An option granted at the money has an exercise price equal to market price yet still has real value.
+Summary
+Measure an equity-classified award at grant-date fair value and leave that measurement alone. Only liability awards are remeasured.</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>22. Stock-Based Compensation</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>IA-SBC-02</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>On January 1, Year 1, Aldridge Corp. grants 20,000 stock options to employees. Each option has a grant-date fair value of $6. The options vest at the end of four years of continued service, and no forfeitures are expected.
+What compensation expense should Aldridge recognize for Year 1?</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>$30,000</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>$60,000</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>$120,000</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>B. $30,000</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>Spreading Option Cost Over the Service Period
+Explanation
+Total compensation cost is set at the grant date and then recognized over the requisite service period, which is the period the employee must work to earn the award. Here that period is four years.
+Working
+Total compensation cost = 20,000 options x $6 grant-date fair value = $120,000
+Annual expense = $120,000 / 4 years = $30,000
+The offsetting credit is to additional paid-in capital, because the company will settle the award in its own shares.
+Why Other Options Are Incorrect
+$120,000 - Incorrect. This expenses the entire award in the year of grant. The employees have not yet rendered the four years of service the award pays for.
+$60,000 - Incorrect. This spreads the cost over two years rather than the four-year vesting period.
+$0 - Incorrect. Cost is recognized as the service is rendered, not deferred until the options are exercised. Many options are never exercised, yet the service was still received.
+Summary
+Total cost of $120,000 is fixed at grant and spread across the four-year service period, so Year 1 expense is $30,000.</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>22. Stock-Based Compensation</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>IA-SBC-03</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>On January 1, Year 1, Bellhaven Inc. grants 12,000 shares of restricted stock to an executive when the market price is $30 per share. The shares vest after three years of continued service.
+What compensation expense should Bellhaven recognize for Year 1?</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>$120,000</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>$180,000</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>$360,000</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>B. $120,000</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>Restricted Stock Follows the Same Pattern as Options
+Explanation
+Restricted stock is measured the same way as any equity-classified award: grant-date fair value, recognized over the service period. For a full-value share award the grant-date fair value is simply the market price of the share, because the employee receives the whole share rather than the right to buy one.
+Working
+Total compensation cost = 12,000 shares x $30 market price at grant = $360,000
+Annual expense = $360,000 / 3 years = $120,000
+Why Other Options Are Incorrect
+$360,000 - Incorrect. This recognizes the full award in the first year. The executive must complete three years of service to earn it.
+$180,000 - Incorrect. This spreads the cost over two years rather than the three-year vesting period.
+$0 - Incorrect. The shares are restricted, not absent. Service is being rendered from the grant date, so cost is recognized from the grant date.
+Summary
+Grant-date value of $360,000 spread over the three-year vesting period gives $120,000 of expense in Year 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>22. Stock-Based Compensation</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>IA-SBC-04</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>What is the effect on total stockholders' equity of recording the annual compensation expense for an equity-classified stock option award?</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Total stockholders' equity increases by the amount of the expense.</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Total stockholders' equity decreases by the amount of the expense.</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>There is no effect on total stockholders' equity.</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>The effect depends on whether the options are in the money at year-end.</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>C. There is no effect on total stockholders' equity.</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>Why the Entry Does Not Change Total Equity
+Explanation
+The entry debits compensation expense and credits additional paid-in capital. Both sides land inside stockholders' equity, so they offset.
+The expense reduces net income and therefore retained earnings. The credit increases additional paid-in capital by the same amount. The composition of equity shifts, but the total does not move.
+The Underlying Logic
+No cash leaves the company and no liability is created. The company is paying for services with a claim on its own equity, so the transaction reshuffles equity rather than reducing it. This is also why cash flow from operations is unaffected, and why the expense is added back as a non-cash item in the indirect method.
+Why Other Options Are Incorrect
+Total equity decreases - Incorrect. This sees the expense but misses the offsetting credit to paid-in capital.
+Total equity increases - Incorrect. Nothing has been contributed. No shares have been issued and no cash received.
+It depends on whether the options are in the money - Incorrect. An equity-classified award is not remeasured after grant, so the share price at year-end does not affect the entry.
+Summary
+Retained earnings falls and paid-in capital rises by the same amount, leaving total stockholders' equity unchanged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>22. Stock-Based Compensation</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>IA-SBC-05</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Which journal entry records the annual compensation cost of an equity-classified stock option award?</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Debit Compensation Expense; Credit Cash</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Debit Compensation Expense; Credit Stock Option Liability</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Debit Additional Paid-In Capital; Credit Compensation Expense</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Debit Compensation Expense; Credit Additional Paid-In Capital - Stock Options</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>D. Debit Compensation Expense; Credit Additional Paid-In Capital - Stock Options</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>Recording the Annual Cost
+Explanation
+Compensation expense is debited because the company has consumed employee services during the period. The credit goes to additional paid-in capital, because the award will be settled in the company's own shares.
+Nothing is paid and nothing is owed in cash, so neither Cash nor a liability belongs in the entry. The credit sits in paid-in capital until the options are exercised or expire.
+Why Other Options Are Incorrect
+Credit Cash - Incorrect. No cash changes hands when the cost is recognized. Cash moves only if and when an employee exercises, and then it flows into the company.
+Credit a Stock Option Liability - Incorrect. A liability arises only for awards that will be settled in cash, such as cash-settled stock appreciation rights. An award settled in shares is an equity instrument.
+Debit Additional Paid-In Capital and credit Compensation Expense - Incorrect. This reverses the entry, reducing paid-in capital and increasing income for services the company consumed.
+Summary
+Debit Compensation Expense and credit Additional Paid-In Capital. The cost is real, but it is settled in equity rather than cash.</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>22. Stock-Based Compensation</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>IA-SBC-06</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Corvale Company grants stock appreciation rights that entitle employees to a cash payment equal to the increase in the company's share price over the grant-date price. How should Corvale account for these awards?</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>As an equity award measured once at grant-date fair value</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>As an equity award measured at intrinsic value on the exercise date</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>As a liability award remeasured to fair value at each reporting date until settlement</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>As a disclosure only, since no shares will be issued</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>C. As a liability award remeasured to fair value at each reporting date until settlement</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>Cash Settlement Makes the Award a Liability
+Explanation
+Classification follows how the award will be settled. Corvale must hand over cash whose amount depends on its own share price, so it has an obligation to transfer assets. That is a liability, not an equity instrument.
+Because the obligation changes as the share price moves, a liability award is remeasured to fair value at every reporting date. Each remeasurement adjusts compensation expense, so the expense recorded over the life of the award moves up and down with the share price.
+The Contrast With an Equity Award
+An equity-classified award is measured once at grant and never revisited, because settling in shares creates no obligation to transfer assets. That single difference in settlement drives a completely different pattern of expense.
+Why Other Options Are Incorrect
+An equity award measured at grant-date fair value - Incorrect. This is the treatment for share-settled awards. Cash settlement creates an obligation that must be carried at its current amount.
+An equity award measured at intrinsic value on exercise - Incorrect. Classification is wrong, and waiting until exercise would leave the obligation unrecorded in the meantime.
+Disclosure only - Incorrect. A probable, measurable obligation to pay cash is recognized, not merely disclosed.
+Summary
+Settlement in cash makes these rights a liability, remeasured to fair value each reporting date, so expense moves with the share price.</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>22. Stock-Based Compensation</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>IA-SBC-07</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Delmont Corp. grants options that vest only if the employee remains employed for three years from the grant date. Over what period should Delmont recognize the compensation cost?</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Over the three-year requisite service period</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Over the contractual ten-year life of the options</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Entirely in the period the options are granted</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>Entirely in the period the options are exercised</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>A. Over the three-year requisite service period</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>The Service Period, Not the Option's Life
+Explanation
+Compensation cost is recognized over the requisite service period: the period during which the employee must work to earn the award. The service condition here is three years of continued employment, so the cost is spread across those three years.
+The contractual life of an option, often ten years, is the window in which a vested option may be exercised. That window is a feature of the instrument and is already reflected in the grant-date fair value. It is not the period over which the employee earns the award.
+Why Other Options Are Incorrect
+Over the contractual ten-year life - Incorrect. This confuses how long an option can be exercised with how long the employee must work to earn it. The exercise window is already priced into the grant-date fair value.
+Entirely in the period of grant - Incorrect. Expensing at grant would charge income before the employee has rendered any of the service the award pays for.
+Entirely in the period of exercise - Incorrect. Exercise is the employee's own timing decision and may never happen. The company received the services regardless.
+Summary
+Spread the cost over the requisite service period, which is the three years the employee must work, not the option's contractual life.</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>22. Stock-Based Compensation</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>IA-SBC-08</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>An employee holding unvested stock options that carry only a service condition resigns before the vesting date. What happens to the compensation cost already recognized for that employee's award?</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>It remains in expense, because the services were received in prior periods.</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>It is reclassified from additional paid-in capital to retained earnings.</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>It is reported as a prior period adjustment to the earliest year presented.</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>It is reversed, because the service condition was never satisfied.</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>D. It is reversed, because the service condition was never satisfied.</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>Failing a Service Condition Reverses the Cost
+Explanation
+An award with only a service condition is earned by working through the vesting period. If the employee leaves first, the condition is never met and the award is forfeited. The employee never earns it, so the company ends up paying nothing for it.
+Cost recognized in earlier periods was based on the expectation that the award would vest. When that expectation fails, the previously recognized compensation cost is reversed in the period of forfeiture.
+Where Market Conditions Differ
+The reversal applies to service and performance conditions. It does not apply to a market condition, such as a target share price. A market condition is built into the grant-date fair value, so cost is recognized for an employee who renders the required service even if the share price target is never reached.
+Why Other Options Are Incorrect
+It remains in expense - Incorrect. The services were received, but the award compensating them was forfeited, so the company bears no cost for it.
+Reclassified to retained earnings - Incorrect. Forfeiture is a current-period reversal of expense, not a movement between equity accounts.
+Reported as a prior period adjustment - Incorrect. A prior period adjustment corrects an error. Recognizing cost on an award then expected to vest was not an error.
+Summary
+A forfeited service-condition award has its previously recognized cost reversed. Market conditions are the exception, because they are priced in at grant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>22. Stock-Based Compensation</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>IA-SBC-09</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>On January 1, Year 1, Thornbury Ltd. grants 50,000 options with a grant-date fair value of $4 each. The options vest after four years of service, and the company estimates that 10% of the options will be forfeited before vesting.
+What compensation expense should Thornbury recognize for Year 1?</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>$45,000</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>$50,000</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>$180,000</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>$200,000</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>A. $45,000</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>Recognizing Cost Only for Awards Expected to Vest
+Explanation
+Compensation cost is based on the number of awards expected to vest, not the number granted. A company that expects some employees to leave before vesting should not recognize cost for awards it does not expect to deliver.
+Working
+Options expected to vest = 50,000 x (100% - 10%) = 45,000 options
+Total compensation cost = 45,000 x $4 = $180,000
+Annual expense = $180,000 / 4 years = $45,000
+If the estimate later proves wrong, the company revises it and adjusts the cumulative expense in the period of the change, treating it as a change in estimate.
+Why Other Options Are Incorrect
+$50,000 - Incorrect. This ignores the forfeiture estimate, using all 50,000 options and $200,000 of total cost over four years.
+$180,000 - Incorrect. This is the total expected cost over the whole four-year period, not the amount for one year.
+$200,000 - Incorrect. This is the total cost with no forfeiture adjustment, and is the whole vesting period rather than a single year.
+Summary
+Apply the forfeiture estimate first, then spread the result over the service period: 45,000 options at $4 over four years is $45,000 a year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>22. Stock-Based Compensation</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>IA-SBC-10</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Which of the following does NOT affect the amount of compensation cost recognized for an equity-classified stock option award?</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>The grant-date fair value of each option</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>The number of options expected to vest</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>The length of the requisite service period</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>The change in the company's share price after the grant date</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>D. The change in the company's share price after the grant date</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>What Is Fixed at Grant and What Is Not
+Explanation
+Total compensation cost for an equity-classified award is the grant-date fair value multiplied by the number of awards expected to vest, recognized across the requisite service period. Those three inputs determine both the total and its timing.
+The share price after the grant date is deliberately excluded. The company will settle in its own shares, so it takes on no further obligation when the price moves. Measurement is fixed at grant and is not revisited.
+A Consequence Worth Knowing
+A company can record the same compensation expense whether its shares triple or collapse after the grant. Employees may end up with something worth far more or nothing at all, while the income statement shows the value the award had on the day it was granted.
+Why Other Options Are Incorrect
+The grant-date fair value - Incorrect. This is the per-option measurement that sets the total cost.
+The number of options expected to vest - Incorrect. Cost is recognized only for awards expected to vest, so this scales the total directly.
+The requisite service period - Incorrect. This sets how many periods the total is spread across, and so determines the annual expense.
+Summary
+Grant-date fair value, awards expected to vest, and the service period drive the cost. Later share price movements do not, because an equity award is never remeasured.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I201"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Intermediate Accounting Selected MCQs.xlsx
+++ b/Intermediate Accounting Selected MCQs.xlsx
@@ -4856,7 +4856,7 @@
 Key Takeaways
 The Mailing Requirement: For a payment to be considered "disbursed," the check must be out of the control of the company. Held checks must be added back to the cash balance.
 Control over Assets: If you can still walk to a desk and tear up the check, the cash is still yours.
-Adjusted Book Balance: On the CPA exam, always check if "book balance" items meet the criteria for recognition before reporting them on the financial statements.
+Adjusted Book Balance: Check that each "book balance" item actually meets the criteria for recognition before it is reported on the financial statements.
 The correct amount to report as cash on Grey's December 31, Year 1, balance sheet is $13,800.</t>
         </is>
       </c>
@@ -7278,8 +7278,8 @@
 Accumulated Depreciation at December 31, Year 7: $900,000
 Key Principle: Prospective Treatment for Estimate Revisions
 Under US GAAP (ASC 250), a change in an asset's useful life or depreciation method is classified as a change in accounting estimate. Changes in estimates are handled strictly with prospective application. This means you do not go back to restate prior years, nor do you need to know the original useful life or how many years the asset has already been in service.
-💡 CPA Exam Tip: Intentional Missing Information
-Exam questions intentionally omit the original useful life or purchase date to test whether you realize they are irrelevant. Because prospective accounting only looks forward, the pre-existing accumulated depreciation ($700,000) gives you everything you need to calculate the current book value.
+Why the Original Useful Life Is Not Given
+The original useful life and the purchase date are not needed here, which is why neither is provided. Because a revised estimate is applied prospectively, only the position today matters: the accumulated depreciation of $700,000 is enough to give the current book value, and the history of the asset never enters the calculation.
 Step-by-Step Calculations
 Step 1: Determine Net Book Value on Reestimate Date (January 1, Year 7)
 | Original Machinery Historical Cost
